--- a/results/Int All Data -0.0/Rando_fi_explain.xlsx
+++ b/results/Int All Data -0.0/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001281243910978541</v>
+        <v>0.0002140888211795977</v>
       </c>
       <c r="C3" t="n">
-        <v>-5.832649812752555e-05</v>
+        <v>-9.28036667422749e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002181476892731704</v>
+        <v>-0.0002940984835211713</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002799557835900623</v>
+        <v>-0.0003698818658788927</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0004114947657465107</v>
+        <v>-0.0006453349497458817</v>
       </c>
       <c r="G3" t="n">
-        <v>6.507539072192261e-05</v>
+        <v>0.000379217758279101</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001061671558729666</v>
+        <v>0.0005565455997292602</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00175265657809762</v>
+        <v>0.0002056769634538291</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0002659938589094368</v>
+        <v>-0.0001206703674513465</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0001438660055461271</v>
+        <v>0.0003574493391150613</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001560380020402352</v>
+        <v>8.35212062677573e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003511076526959788</v>
+        <v>-0.0001763310416525832</v>
       </c>
       <c r="N3" t="n">
-        <v>-5.246067197496049e-05</v>
+        <v>8.914554492970091e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0005311941478310723</v>
+        <v>-0.0004951158464493499</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0004043599940487009</v>
+        <v>2.067085595519559e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003020706389833999</v>
+        <v>0.0001561355516264674</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0003855663062526682</v>
+        <v>0.000709651632469217</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008898478515981868</v>
+        <v>0.0004538681015865076</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0002407308064422253</v>
+        <v>0.0002271863626692649</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0005583909892198622</v>
+        <v>-0.0005698593266588291</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001979677410878833</v>
+        <v>-0.0002396590286489641</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001820042628469936</v>
+        <v>-0.001201689235244649</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.0002154784596461101</v>
+        <v>0.0009605945177720142</v>
       </c>
       <c r="Y3" t="n">
-        <v>-9.064936407169099e-05</v>
+        <v>0.0002979722764898551</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001611940704760955</v>
+        <v>0.0007865046401418508</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003029952219103186</v>
+        <v>0.002185844290988289</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.001012367885017642</v>
+        <v>0.0002164651699814823</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.0002398730430538187</v>
+        <v>0.0003153629899228428</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.007870862377588267</v>
+        <v>0.006340945107581514</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.004318341084365586</v>
+        <v>0.003342310458343727</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0002417147990320567</v>
+        <v>-0.000994593784920872</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.0001126567599207462</v>
+        <v>2.554087796620365e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>4.840094850549927e-05</v>
+        <v>7.313973753041991e-05</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0004348314425619127</v>
+        <v>-0.0002718959620700912</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.0008280531706046935</v>
+        <v>-0.002943354059987726</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.007804834162633162</v>
+        <v>0.005047408875249128</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0007960736712704808</v>
+        <v>-0.0001130950695192712</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.004407025499647685</v>
+        <v>0.0009453185436304179</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.001870850763250593</v>
+        <v>0.0005588338750485166</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0001960408253173308</v>
+        <v>0.001644748841027966</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1.973061578487642e-05</v>
+        <v>-0.0003131508731611465</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.003404199426498251</v>
+        <v>0.001844202758082795</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.004927057245728442</v>
+        <v>0.003627854578418883</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0005954386043601212</v>
+        <v>-0.0001967350498779507</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.0004176149466807678</v>
+        <v>-0.0002485327741789088</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.0006131867231752164</v>
+        <v>9.413001596082269e-05</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.001078032963979056</v>
+        <v>-0.000394167535524237</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.833876406703293e-05</v>
+        <v>-0.0004431078893346607</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.199873894090716e-05</v>
+        <v>-0.0003028425318460482</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.0003869310594801523</v>
+        <v>0.0001414217480021595</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.001581794514100876</v>
+        <v>0.0007862770530236684</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.0019214024810553</v>
+        <v>0.001937838399442815</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.003967391541511496</v>
+        <v>0.004072534823495575</v>
       </c>
       <c r="BC3" t="n">
-        <v>-8.136019711855183e-06</v>
+        <v>-0.000109404834465906</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.001896784216811e-05</v>
+        <v>-0.0001468380938541947</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0006994027100041455</v>
+        <v>-4.038813775449904e-05</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.002272063511139197</v>
+        <v>0.001540015431673056</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.002260798239705917</v>
+        <v>0.001993464627475603</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.0007910761447703651</v>
+        <v>0.0008448091840291492</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.003767664950425422</v>
+        <v>0.0009251751694345911</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.000461455938347436</v>
+        <v>-0.0005667323059988106</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.001639682605946757</v>
+        <v>-0.000889763192277283</v>
       </c>
       <c r="BL3" t="n">
-        <v>8.05433860709892e-05</v>
+        <v>0.0002124166055418863</v>
       </c>
       <c r="BM3" t="n">
-        <v>3.27853772096232e-05</v>
+        <v>0.0006019163853365117</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.002736599359664235</v>
+        <v>0.001707551172815304</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.00053412933933068</v>
+        <v>0.0009050660309987557</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.0008680130709313791</v>
+        <v>-0.002233074912744412</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0002482348220435893</v>
+        <v>-0.001036659799223624</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0009108326465401617</v>
+        <v>-0.0001490172416638391</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.00153587793505065</v>
+        <v>0.000673214618580471</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.0003290787888409597</v>
+        <v>0.0007349897421001261</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.0003999467244203115</v>
+        <v>-0.001336731624907689</v>
       </c>
       <c r="BW3" t="n">
-        <v>-3.826332793268717e-05</v>
+        <v>3.314085022849689e-06</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.0005381961380703772</v>
+        <v>0.0001104874532911548</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.0008223673323834102</v>
+        <v>-6.952495891111796e-05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.002375217726288592</v>
+        <v>0.001243919308385215</v>
       </c>
       <c r="CA3" t="n">
-        <v>-5.458496201706245e-05</v>
+        <v>-0.0001887397474216212</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0007112403190570971</v>
+        <v>0.0004515339254436135</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.0006996705530764658</v>
+        <v>-0.0006039979919253635</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.0008559307470791977</v>
+        <v>-4.408908975085946e-05</v>
       </c>
       <c r="CE3" t="n">
-        <v>8.433697632706181e-05</v>
+        <v>0.0002707068938222545</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.001514500146033767</v>
+        <v>-0.0002288562740236166</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.001853975060674134</v>
+        <v>-0.0005779977519542457</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0004279206352091481</v>
+        <v>-0.0004263640944115387</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.00119205499100304</v>
+        <v>-0.0009958883208317526</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-3.138005192513281e-05</v>
+        <v>-2.796623202191651e-05</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0008358244076939159</v>
+        <v>-0.0003426377839835327</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.0008923169735184944</v>
+        <v>-0.0008257661325474253</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.0001243224833220313</v>
+        <v>7.817426413724405e-05</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0004371750392227503</v>
+        <v>-0.0002238479118016978</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.0004781722766574991</v>
+        <v>0.0001086209088133805</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.0003091832757301816</v>
+        <v>0.0001099985944563886</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.0002352025630535892</v>
+        <v>-0.0003560815452581578</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.0002040838098555119</v>
+        <v>-0.0007636565897659898</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.0001552500228195885</v>
+        <v>-0.002609648711169306</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.001151462619443224</v>
+        <v>-0.002135021785605104</v>
       </c>
       <c r="CU3" t="n">
-        <v>-1.533357472552789e-05</v>
+        <v>-4.708657803651476e-06</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.0001194066218529055</v>
+        <v>-8.099974266019051e-05</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.001304449419983533</v>
+        <v>-0.000553432727331875</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.001128803416100823</v>
+        <v>-0.0008529672262269482</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-5.879653642422711e-05</v>
+        <v>-0.0001048230879269562</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0.0001446472185581582</v>
+        <v>-2.548431485319135e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0.0003671752265526762</v>
+        <v>-0.0003108918283490902</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0.001044107905538269</v>
+        <v>-0.0002604459717150476</v>
       </c>
       <c r="DD3" t="n">
-        <v>-0.0001493653369400805</v>
+        <v>0.0001320877650613894</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0002105970858552486</v>
+        <v>0.0003032913657057679</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.000929933547187798</v>
+        <v>8.894394151588448e-06</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.0001641723111557036</v>
+        <v>-0.0007195864826348352</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.001622542283877632</v>
+        <v>-0.002425699619382927</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.0004997761971907376</v>
+        <v>-3.664234790547113e-05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.0003614645347209466</v>
+        <v>-0.001584374774616877</v>
       </c>
       <c r="DK3" t="n">
-        <v>-6.880516911010991e-05</v>
+        <v>-0.0001693110971202383</v>
       </c>
       <c r="DL3" t="n">
-        <v>-1.221920773668451e-05</v>
+        <v>3.532773484094421e-05</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0.0006453239721767468</v>
+        <v>-0.0004372509066955843</v>
       </c>
       <c r="DN3" t="n">
-        <v>9.098357018976974e-05</v>
+        <v>-0.0007231777761903334</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.001016523756554784</v>
+        <v>-0.001926030175840975</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.0008148725792756518</v>
+        <v>-0.001413794369650489</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-3.692187374636835e-05</v>
+        <v>-0.0001691277370416089</v>
       </c>
       <c r="DR3" t="n">
-        <v>-6.94487725024928e-05</v>
+        <v>-0.0002647161741823445</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.0001081412309450069</v>
+        <v>-0.0001497104748506639</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.001970069150308152</v>
+        <v>-0.002624417453314328</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0.0006723324394035657</v>
+        <v>-0.001201626788155896</v>
       </c>
       <c r="DV3" t="n">
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>1.625135159676883e-05</v>
+        <v>-0.0001562886839212397</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.0004251727392163774</v>
+        <v>-0.0002561137435733796</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.001491195100140919</v>
+        <v>-0.002457595219168892</v>
       </c>
       <c r="DZ3" t="n">
-        <v>-4.631484990599177e-05</v>
+        <v>-5.249603126313952e-05</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.0005851566951635323</v>
+        <v>-0.0002805843107153849</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.003290824339606668</v>
+        <v>-0.001506151920646951</v>
       </c>
       <c r="EC3" t="n">
-        <v>-6.357890751436225e-05</v>
+        <v>2.731427741798893e-06</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0.0009778412174104888</v>
+        <v>-0.0002022965831793644</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.0002200403658393924</v>
+        <v>4.357622915036718e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.001215102207225451</v>
+        <v>-0.0005766118985445591</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.001022884578363095</v>
+        <v>-0.0001347138463199161</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.0001188416382289681</v>
+        <v>0.0002300676460419582</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0.0008946144749329129</v>
+        <v>-0.000237402577535194</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0003659412551651819</v>
+        <v>-0.0004824400631651016</v>
       </c>
       <c r="EK3" t="n">
-        <v>-2.364562839151991e-05</v>
+        <v>-0.0002439178168123457</v>
       </c>
       <c r="EL3" t="n">
-        <v>-3.368149559332956e-06</v>
+        <v>-6.181086338046592e-05</v>
       </c>
       <c r="EM3" t="n">
-        <v>8.905987935138194e-05</v>
+        <v>-3.804306055007811e-05</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.0003170630581758805</v>
+        <v>0.0001639788648127971</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.0005362603320651861</v>
+        <v>0.0005214879643484826</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.0007092744421009389</v>
+        <v>0.0001185238233784158</v>
       </c>
       <c r="ER3" t="n">
-        <v>1.948586340945857e-05</v>
+        <v>-3.669316234191866e-05</v>
       </c>
       <c r="ES3" t="n">
-        <v>-6.365622321736984e-05</v>
+        <v>1.018076721224226e-05</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.0003346658403909263</v>
+        <v>-0.0005696825257613881</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0.0007498816768400951</v>
+        <v>-0.000178447272708262</v>
       </c>
       <c r="EV3" t="n">
-        <v>-3.193777539139186e-05</v>
+        <v>-2.382151530810118e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>-1.739587350943925e-05</v>
+        <v>0.0002660620038382588</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.0001608270040746884</v>
+        <v>-8.578313173779663e-05</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.0004987482743394467</v>
+        <v>-0.0008492489443310258</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003979980788943287</v>
+        <v>0.003169080201290877</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001101701426139945</v>
+        <v>0.0009922568123224306</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001168473188713427</v>
+        <v>0.0008190885762905463</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002543175635404337</v>
+        <v>0.0007353495108037148</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0005449944658003287</v>
+        <v>0.0005551149443722193</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004257111001932854</v>
+        <v>0.003072062454095646</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001271061823328998</v>
+        <v>0.001392671892696961</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004369271356314188</v>
+        <v>0.002293291165625641</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002491397365230616</v>
+        <v>0.002331248578654319</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001120472180223283</v>
+        <v>0.0008888386907866079</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005692509265364848</v>
+        <v>0.0005704612784715402</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001447946415913877</v>
+        <v>0.001673168398499349</v>
       </c>
       <c r="N4" t="n">
-        <v>0.008308595266514956</v>
+        <v>0.005223537829315961</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003186664652240464</v>
+        <v>0.002661233900962549</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001873316968897383</v>
+        <v>0.00158639433562688</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007072002540940256</v>
+        <v>0.003837488621659651</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001887060559487501</v>
+        <v>0.001927788000542805</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003944672909386541</v>
+        <v>0.002913803546854325</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001008968631631778</v>
+        <v>0.0008102386327308804</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002299064048868826</v>
+        <v>0.001802197014546478</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002732324923394403</v>
+        <v>0.004097777600355213</v>
       </c>
       <c r="W4" t="n">
-        <v>0.00205277641629534</v>
+        <v>0.002668754055168552</v>
       </c>
       <c r="X4" t="n">
-        <v>0.003851848000754557</v>
+        <v>0.004783364230232692</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001215463605330928</v>
+        <v>0.001176388044427443</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.003833906619300921</v>
+        <v>0.003747340117867141</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.008301881493507055</v>
+        <v>0.002534227245208787</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002068930810863932</v>
+        <v>0.0007874847191130248</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.004076775419547297</v>
+        <v>0.002477061148257334</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.00705628875358451</v>
+        <v>0.007280810417945715</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.009637769284010226</v>
+        <v>0.01144483036864369</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.00303074780438012</v>
+        <v>0.004990958272217602</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.00191030609961075</v>
+        <v>0.0006867344476323179</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.000903240959024925</v>
+        <v>0.0009968836819594729</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.003134293100529773</v>
+        <v>0.001290470750361124</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.008655720369345473</v>
+        <v>0.009567656036445271</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01399607151527239</v>
+        <v>0.01229190958615813</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.002806753647573548</v>
+        <v>0.001192062379062955</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.004348552738483803</v>
+        <v>0.003864225933184766</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.00257136907774091</v>
+        <v>0.002226854440458464</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.003237582629669015</v>
+        <v>0.006858494575654918</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001700480884700199</v>
+        <v>0.0009559300997717207</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.005925177939530984</v>
+        <v>0.004582203458207279</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.01168359878887936</v>
+        <v>0.0100928081628649</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0017407598247575</v>
+        <v>0.001910516278877935</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.003040478204017883</v>
+        <v>0.003133735529446227</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.002277996995848424</v>
+        <v>0.001434963485824507</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.00146128689977273</v>
+        <v>0.001906022013352227</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.001605881292040212</v>
+        <v>0.002630381024623761</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0007698691283056206</v>
+        <v>0.000674902784320151</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.002581930293023463</v>
+        <v>0.002298200885911877</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.002977378577991916</v>
+        <v>0.001769082523378824</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.00750453062804683</v>
+        <v>0.003798404346711632</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.002939427573663661</v>
+        <v>0.002502518522046311</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0005851759092443575</v>
+        <v>0.0005358680860866921</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.001132290459659304</v>
+        <v>0.0004297359149573817</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.004048170437491217</v>
+        <v>0.002310721213036107</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.003206634855227255</v>
+        <v>0.002606349604537515</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.003897686367571163</v>
+        <v>0.001844296793747945</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001371330759550823</v>
+        <v>0.001944864404290803</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0050960029125075</v>
+        <v>0.003925101659107433</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.003803175216406998</v>
+        <v>0.002968329574078644</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.003145251363624419</v>
+        <v>0.003516843920377045</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0009310884396512808</v>
+        <v>0.0008181571254178518</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.001729680941259262</v>
+        <v>0.002289282788624887</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.009328793133505651</v>
+        <v>0.003601684608560983</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.003340941786853316</v>
+        <v>0.00267733605358161</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.002774898517442331</v>
+        <v>0.005328661998284684</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.002327182444813696</v>
+        <v>0.003467410566125411</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.00206432582237174</v>
+        <v>0.00100548316036129</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.00148411718391733</v>
+        <v>0.001853505078535252</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.002325859924541912</v>
+        <v>0.001659947593782716</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003354553787830622</v>
+        <v>0.003382557033455914</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.444662753722184e-05</v>
+        <v>1.960674085464523e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.004176297743943545</v>
+        <v>0.002400390591926175</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.003138114933173993</v>
+        <v>0.002351857280408298</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.004614400474848047</v>
+        <v>0.002478054878316632</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.001464836345389709</v>
+        <v>0.001401847234169947</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.002345355008575412</v>
+        <v>0.0006964320995509857</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.004117952232272406</v>
+        <v>0.0008935368802934856</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.002203993051500487</v>
+        <v>0.003378471986765664</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.001445449925769393</v>
+        <v>0.001982335694587748</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.002167098343661173</v>
+        <v>0.00187639404099993</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.003917581149454187</v>
+        <v>0.002147888921773484</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0008451823448266735</v>
+        <v>0.00246154551512832</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.002405450512799777</v>
+        <v>0.002509814042991804</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0001717573032994671</v>
+        <v>0.0001173942517110008</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.002121589833285351</v>
+        <v>0.001584568118462534</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.00133575895695083</v>
+        <v>0.002889128395901067</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.001381048258374502</v>
+        <v>0.0004716118729351939</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0008910396789826696</v>
+        <v>0.0008699022324289188</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.001523284150176299</v>
+        <v>0.001439186187732146</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0006973152666102297</v>
+        <v>0.0002274610867825061</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.001587712390513862</v>
+        <v>0.002336917521931093</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.003223007240425806</v>
+        <v>0.002762649766666655</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.004579700923324641</v>
+        <v>0.003327608642100764</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.003363758727501537</v>
+        <v>0.003360798394965878</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0004434007602183079</v>
+        <v>0.0002918980309693857</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0003762486339868215</v>
+        <v>0.0003671407111913381</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.003612751407018398</v>
+        <v>0.00137217887509527</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.002972998244184032</v>
+        <v>0.00297397795450046</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0004358657862551301</v>
+        <v>0.000705823249829874</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0004367996090906046</v>
+        <v>0.0002590849295684537</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.001206394954847278</v>
+        <v>0.0006005004992196124</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.002909898619489041</v>
+        <v>0.001765010167719073</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0007801051946474658</v>
+        <v>0.0002822142554715376</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.001433459180105236</v>
+        <v>0.001145016213520208</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.002659914532696541</v>
+        <v>0.00105082083475115</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.001578657052478363</v>
+        <v>0.002313646836204523</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.002847319136630599</v>
+        <v>0.002969542060541158</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.002462794645582537</v>
+        <v>0.001176333203300968</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.00271081220679238</v>
+        <v>0.003877818529171146</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.001778710825235624</v>
+        <v>0.00130118092679515</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0002875409251924927</v>
+        <v>0.0001796151712002072</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.001119996401143681</v>
+        <v>0.001299537239552039</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.004109485235951435</v>
+        <v>0.0025141748976617</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.001872184226404467</v>
+        <v>0.002608985725764796</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.00309230832185134</v>
+        <v>0.002924767887725032</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0006740580678119275</v>
+        <v>0.0005447853115880141</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0003130652553174118</v>
+        <v>0.0007552264154191358</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.000355875136586708</v>
+        <v>0.0004895555843854141</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.002977808370142983</v>
+        <v>0.004261398488193902</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.003755256864209532</v>
+        <v>0.004034841510277795</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0004259251193602993</v>
+        <v>0.0004203162253583415</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.002077897094427291</v>
+        <v>0.00114032898703847</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.002499440201646914</v>
+        <v>0.003358041563454836</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0005878357596839549</v>
+        <v>0.0003271866502641137</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.001360512474421106</v>
+        <v>0.00193326760039909</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.004786340215248016</v>
+        <v>0.001828498536497196</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.001404845438765056</v>
+        <v>0.0009628438973177109</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.002506885613669849</v>
+        <v>0.0008253365243366473</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0004119595404068179</v>
+        <v>0.0002093930390641763</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.001935108947279445</v>
+        <v>0.0009239388826680538</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.001995127727224039</v>
+        <v>0.001109629203189022</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0004942884549008038</v>
+        <v>0.0006398456636498696</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.002525023486365973</v>
+        <v>0.001155893610873263</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.001125023151306244</v>
+        <v>0.001367155459117267</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.001523336922288796</v>
+        <v>0.001536211364295642</v>
       </c>
       <c r="EL4" t="n">
-        <v>1.908042986297954e-05</v>
+        <v>0.0001001448163457548</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0002459522513160676</v>
+        <v>0.0002681125584201908</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0004799343617998188</v>
+        <v>0.0003146331081440039</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0007752271387211361</v>
+        <v>0.0007244237481191342</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.001444021456080796</v>
+        <v>0.001343013379802817</v>
       </c>
       <c r="ER4" t="n">
-        <v>5.09295929777865e-05</v>
+        <v>9.54612652423067e-05</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0006297208212838478</v>
+        <v>7.56694278714264e-05</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.001290319357576594</v>
+        <v>0.001075365885379365</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.002247186866996869</v>
+        <v>0.001526611348762524</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0001562212090969583</v>
+        <v>0.0005218346371201269</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.001235569219253867</v>
+        <v>0.001180212073646219</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.001087732554857292</v>
+        <v>0.001027180714643801</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.001193165842313307</v>
+        <v>0.0008595994044236571</v>
       </c>
     </row>
     <row r="5">
@@ -2614,466 +2614,466 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.004451612903225821</v>
+        <v>-0.004483870967741954</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.001242027526015466</v>
+        <v>-0.002081235313863727</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0014021887824897</v>
+        <v>-0.002096774193548412</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0025316455696202</v>
+        <v>-0.001285168461271247</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.00138408304498272</v>
+        <v>-0.001477005706612999</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.004169769173492144</v>
+        <v>-0.004048318641854354</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0002778742618965158</v>
+        <v>-0.001354637026745387</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.003681833970128578</v>
+        <v>-0.003390399462907023</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.005300957592339217</v>
+        <v>-0.003155421282309512</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.001612903225806461</v>
+        <v>-0.0007508978126019916</v>
       </c>
       <c r="L5" t="n">
+        <v>-0.0008392077878482951</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.002709677419354861</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.006915072171869774</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.004903225806451616</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.002252693437806041</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.005158341495266039</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.001926216127979097</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.002535602639805457</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.001389371309482434</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.004584925321292089</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.009968739145536665</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.004765450483991118</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.007903225806451619</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.001245674740484448</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.005190311418685156</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-7.032348804495437e-05</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.0006252170892670605</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0.004619659604029158</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.00406451612903227</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-0.02116129032258065</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.01045161290322583</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-0.0006774193548387153</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.0007049345417925679</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.001870967741935503</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.02577419354838711</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.01164516129032261</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.002551191675058773</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-0.005677419354838708</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.003741935483870995</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.009129032258064529</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.002118791246960705</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.002322580645161321</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.01151612903225809</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-0.003499627699181018</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-0.005570934256055404</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0.00277874261896488</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-0.004935483870967761</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-0.005096774193548414</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-0.001322580645161297</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-0.004290657439446422</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-0.001111497047585974</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-0.005536332179930836</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-0.0009141364675154696</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-0.0009575923392612706</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-0.000903225806451613</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-0.002629757785467168</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-0.003451612903225809</v>
+      </c>
+      <c r="BG5" t="n">
         <v>-0.00103806228373704</v>
       </c>
-      <c r="M5" t="n">
-        <v>-0.002041522491349512</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-0.01045501910385556</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-0.005279610976033388</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.004035567715458243</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.005872011251758136</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-0.002629757785467168</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.0052796109760334</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.001946962067807978</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.00519354838709678</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-0.00569642236887814</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-0.001599738818152074</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.00767741935483871</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-0.002291381668946624</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-0.007172995780590763</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-0.005848153214774254</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-0.005467128027681722</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-0.008139534883720901</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.001424105592219493</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-0.01251612903225808</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-0.004822161422708582</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-0.002967741935483914</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-0.001898734177215122</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-0.005095759233926089</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-0.02422580645161292</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-0.006019151846785198</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-0.00294117647058828</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-0.002257728377909052</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-0.002645161290322595</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-0.005258064516129035</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-0.002047654504839846</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-0.004008438818565441</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-0.0177741935483871</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-0.001225806451612921</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>-0.005731156651615166</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>-0.002320675105485304</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-0.001079672375279162</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>-0.003483870967741942</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>-0.001299589603283147</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>-0.004394463667820136</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-0.00328719723183396</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-0.01118443904133385</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-0.0001389371309482912</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>-0.0009679821295606073</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>-0.001611278952668704</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>-0.007404844290657487</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>-0.002271034996276933</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>-0.003010380622837416</v>
-      </c>
       <c r="BH5" t="n">
-        <v>-0.0007446016381235209</v>
+        <v>-0.001074185968445818</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.001701979854116065</v>
+        <v>-0.003852432255958182</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.009000000000000031</v>
+        <v>-0.00829032258064517</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.006435986159169571</v>
+        <v>-0.007543252595155725</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.002032258064516157</v>
+        <v>-0.0009342560553633362</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.002584759986572682</v>
+        <v>-0.002807704864511895</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.02601597777005911</v>
+        <v>-0.004152249134948149</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.005000000000000016</v>
+        <v>-0.001567091087169425</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.007301038062283738</v>
+        <v>-0.01719723183391008</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.004515456755818004</v>
+        <v>-0.009734810339039968</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.003924973949288002</v>
+        <v>-0.002154582763337875</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.0004244205027750136</v>
+        <v>-0.001563042723167718</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.004256055363321865</v>
+        <v>-0.001319902744008305</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.005743944636678255</v>
+        <v>-0.01076124567474054</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.000207612456747408</v>
+        <v>-3.516174402249383e-05</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.009826989619377202</v>
+        <v>-0.005882352941176516</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.00507120527961098</v>
+        <v>-0.00426317556226925</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.004571026722925498</v>
+        <v>-0.002941176470588292</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.002568875651526381</v>
+        <v>-0.002605071205279574</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.001779120510238341</v>
+        <v>-0.0003126085446335414</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.01072664359861597</v>
+        <v>-0.002448579823702235</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.005745554035567679</v>
+        <v>-0.005326633165829176</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.001863572433192739</v>
+        <v>-0.003536857781087177</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.004636678200692112</v>
+        <v>-0.002987148315387256</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.01224913494809693</v>
+        <v>-0.005840886203424001</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.0009045226130653505</v>
+        <v>-0.006678200692041558</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.004616963064295443</v>
+        <v>-0.007577854671280282</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.000484429065743952</v>
+        <v>-0.0003473428273705892</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.001477005706612977</v>
+        <v>-0.004229607250755297</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.003305203938115364</v>
+        <v>-0.005419523343127619</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.00154414232964083</v>
+        <v>-0.0007988885029524106</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.001077375122428925</v>
+        <v>-0.001180965613060059</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.00187565126780137</v>
+        <v>-0.001458839874956575</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.0005904828065300572</v>
+        <v>-0.0001005025125628167</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.002462380300957556</v>
+        <v>-0.004397448808324956</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.007231833910034613</v>
+        <v>-0.005896147403685104</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.006286905175408164</v>
+        <v>-0.0104550191038555</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.008266759291420667</v>
+        <v>-0.01045501910385547</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0.00100729419937482</v>
+        <v>-0.0005210142410558838</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.000484429065743952</v>
+        <v>-0.0008935219657483451</v>
       </c>
       <c r="CW5" t="n">
         <v>0</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0.00892671066342483</v>
+        <v>-0.002813476901701961</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.003305203938115375</v>
+        <v>-0.005561139028475747</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.0007385028533064997</v>
+        <v>-0.001644847264182647</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0.00121107266435988</v>
+        <v>-0.0002978406552494483</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0.002774193548387116</v>
+        <v>-0.001493574157693611</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0.007537339353942374</v>
+        <v>-0.002345058626465679</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0.001597777005904877</v>
+        <v>-0.000311418685121112</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0.002709677419354861</v>
+        <v>-0.001076762764848904</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.007711010767627658</v>
+        <v>-0.001833910034602104</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0.001812688821752251</v>
+        <v>-0.005438066465256808</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.006851211072664376</v>
+        <v>-0.00789277736411027</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.001806451612903237</v>
+        <v>-0.002084056964223668</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.004221453287197296</v>
+        <v>-0.009493670886076</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0.002606105733432562</v>
+        <v>-0.003090096798213016</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0.0004103967168262446</v>
+        <v>-0.0001054852320674815</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0.002525951557093464</v>
+        <v>-0.002698961937716305</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0.005974296630774601</v>
+        <v>-0.006612957368244387</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.003903225806451616</v>
+        <v>-0.007116482040953343</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.006678200692041558</v>
+        <v>-0.007889273356401416</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.001787043931496579</v>
+        <v>-0.00147058823529409</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.0004839910647802537</v>
+        <v>-0.00212038303693568</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.0007612456747404961</v>
+        <v>-0.00123953098827474</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.00764154220215354</v>
+        <v>-0.01370242214532877</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0.008858131487889298</v>
+        <v>-0.01162629757785473</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0.0006252170892671272</v>
+        <v>-0.001007049345417954</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.004013840830449889</v>
+        <v>-0.001638123603871966</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0.005383813824244554</v>
+        <v>-0.008858131487889298</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.0009725599166377607</v>
+        <v>-0.0007835455435847072</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.00183870967741937</v>
+        <v>-0.005051903114186918</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.01501730103806231</v>
+        <v>-0.004565290365894615</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0.002179930795847784</v>
+        <v>-0.001111497047585963</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0.004935483870967749</v>
+        <v>-0.002382725241995587</v>
       </c>
       <c r="EE5" t="n">
-        <v>-0.0001025991792065639</v>
+        <v>-0.0003350707371556294</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0.004878892733564078</v>
+        <v>-0.00224913494809692</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.004741935483870962</v>
+        <v>-0.002308265078183225</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0.0008087201125176136</v>
+        <v>-0.0006701414743112589</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.003350707371556183</v>
+        <v>-0.002308265078183225</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.002450486740516933</v>
+        <v>-0.003000000000000014</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0.002606105733432562</v>
+        <v>-0.002560553633218032</v>
       </c>
       <c r="EL5" t="n">
-        <v>-3.460207612456801e-05</v>
+        <v>-0.000207612456747408</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0.0001367989056087371</v>
+        <v>-0.0005557485237929427</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0.0001958863858961601</v>
+        <v>-0.0004467609828741726</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.00044459644322844</v>
+        <v>-0.000242214532871976</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0.002674539770753759</v>
+        <v>-0.0009575923392612596</v>
       </c>
       <c r="ER5" t="n">
-        <v>0</v>
+        <v>-0.0002978406552494595</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.001489203276247131</v>
+        <v>-9.677419354839901e-05</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.002967741935483881</v>
+        <v>-0.002709677419354861</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.005096774193548393</v>
+        <v>-0.003350707371556283</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0.0003419972640218649</v>
+        <v>-0.0005813953488372104</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0.001806451612903237</v>
+        <v>-0.001861504095309052</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.0007266435986159281</v>
+        <v>-0.00143650016323863</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.0009725599166377719</v>
+        <v>-0.001980530379321943</v>
       </c>
     </row>
     <row r="6">
@@ -3083,466 +3083,466 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.001479354620859177</v>
+        <v>-0.001432515945221494</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0006153786212747924</v>
+        <v>-9.525199935946638e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>-8.210791374216875e-05</v>
+        <v>-0.0005689654286879064</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.000999191957492729</v>
+        <v>-0.0009814176623298033</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0006773185133727294</v>
+        <v>-0.0009068112616389401</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.001966407042937193</v>
+        <v>-0.001398054880166702</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001005108758651535</v>
+        <v>-0.0001098100330393675</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.001012430043475107</v>
+        <v>-0.00108566006617587</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.001519624869746472</v>
+        <v>-0.001339447156772713</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0003192055635634572</v>
+        <v>-0.000138803491864517</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.442592143304002e-05</v>
+        <v>-0.0001762189392620767</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0006751773182757881</v>
+        <v>-0.001090448352080417</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.004589510486989085</v>
+        <v>-0.003618470946395011</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0003896973528024539</v>
+        <v>-0.001727410864257381</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0002702339670894394</v>
+        <v>-0.0006078499478985533</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.001535303306658401</v>
+        <v>-0.001958783813600459</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.0005876591576885054</v>
+        <v>-0.0003661770289026145</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0007091392635947852</v>
+        <v>-0.001828720769980621</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0008059217730279288</v>
+        <v>-0.0001484032431538163</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.001639009143508513</v>
+        <v>-0.001135141272041423</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0005737812623187344</v>
+        <v>-0.001256190583386729</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0007776115729742378</v>
+        <v>-0.003591544124707588</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.001419631257957746</v>
+        <v>-0.001201329966399545</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.0004434753679082942</v>
+        <v>-0.0001121773059298475</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0002087031613004581</v>
+        <v>-0.001093065196678913</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.004295540796963987</v>
+        <v>6.451612903227989e-05</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.001513825815725262</v>
+        <v>-0.0002046809390345961</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.001409452612140283</v>
+        <v>-0.001050491547096008</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.003324063843585615</v>
+        <v>0.002456461236100796</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.0008611776006201165</v>
+        <v>0.0008361589585227175</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.001615975809158746</v>
+        <v>-0.002861537509709977</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.001298163210553108</v>
+        <v>-0.0004887809665924836</v>
       </c>
       <c r="AH6" t="n">
-        <v>8.161932745667789e-06</v>
+        <v>-0.0005715119961568732</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.001372602027262168</v>
+        <v>-0.001428277488944169</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.0003957927859060878</v>
+        <v>-0.0004232285926237256</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.001527772440131631</v>
+        <v>-0.001593698080657444</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0007837920905409829</v>
+        <v>-0.0007762466000050233</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.001001316040104633</v>
+        <v>-0.001720011075481703</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0003883973544741737</v>
+        <v>-0.0005973730858536668</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.002321045472866034</v>
+        <v>-0.0004449197464113402</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.001591465231059699</v>
+        <v>-0.000449959196231875</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.0001712043331011493</v>
+        <v>-0.001088758348756749</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.0001159255268855268</v>
+        <v>-0.0009841835471637583</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0008466740049197009</v>
+        <v>-0.001130325302844684</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.001585976500411782</v>
+        <v>-0.001344129906217417</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.0009661470749105256</v>
+        <v>-0.0005400079122807294</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.0001722013837643921</v>
+        <v>-0.0008323952355405118</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.0007043412007133653</v>
+        <v>-0.001786460680948088</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0005302515532603802</v>
+        <v>-0.0008185111648335686</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.00218881856540086</v>
+        <v>-0.0008579171755425858</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.264195730679899e-06</v>
+        <v>-0.0008089877797731515</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.0001023254965003273</v>
+        <v>-0.000852689511813054</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.002005547318668402</v>
+        <v>0.002601699936661006</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0001923626677062057</v>
+        <v>-0.0003796330373461943</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0005398061633799412</v>
+        <v>-0.0003139598970334168</v>
       </c>
       <c r="BE6" t="n">
-        <v>-8.092738789470532e-05</v>
+        <v>-0.001739511648338879</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.38405857635749e-05</v>
+        <v>0.000474619649398092</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.0004572525080295653</v>
+        <v>0.0009153014774527845</v>
       </c>
       <c r="BH6" t="n">
-        <v>-3.473428273707557e-05</v>
+        <v>-0.000201710319842438</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0007778714613171783</v>
+        <v>-0.001460628952333754</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0003400136917128121</v>
+        <v>-0.001171329486140113</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.002486659220650323</v>
+        <v>-0.002034564532371786</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0001834040817367461</v>
+        <v>-0.0001503515526147303</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.000614748729314185</v>
+        <v>-0.000804493607771506</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.005390480405568504</v>
+        <v>-0.001471450932353355</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.001497041941392138</v>
+        <v>-0.0009379551545865839</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.0007780880212760633</v>
+        <v>-0.001485458997980671</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.0008897438955868448</v>
+        <v>-0.001263925786474884</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.0001646195257103467</v>
+        <v>-0.0007602444316057666</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.0004113510239371787</v>
+        <v>-0.0002722752983200294</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.0006579434776264105</v>
+        <v>-0.0002579409744468575</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.0003833824468621766</v>
+        <v>-0.0008689480232901781</v>
       </c>
       <c r="BW6" t="n">
-        <v>-3.444278993127714e-05</v>
+        <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.0002341192369036932</v>
+        <v>-0.000228575386586774</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.002595230826736067</v>
+        <v>-0.0001582278481012389</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0007430588858608755</v>
+        <v>3.460207612458743e-05</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0.0005989980452687893</v>
+        <v>-0.001371483671136953</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0003139598970333585</v>
+        <v>-9.893001258000079e-05</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.001944405963739576</v>
+        <v>-0.001194851439963499</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.001191302572478517</v>
+        <v>-0.002058718390590805</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0007272385283721511</v>
+        <v>-0.0003598989617252718</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.002847863108820939</v>
+        <v>-0.001406866150419839</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.002577355549480581</v>
+        <v>-0.001156245352329616</v>
       </c>
       <c r="CH6" t="n">
-        <v>8.744784173397871e-07</v>
+        <v>-0.0006297602664715352</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.003290032295382644</v>
+        <v>-0.001184219640166945</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-2.448579823702002e-05</v>
+        <v>-2.419354838709975e-05</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.000178384567046852</v>
+        <v>-0.0006823507347425012</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.001860935104824859</v>
+        <v>-0.002133586728774559</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.0009350192131426128</v>
+        <v>-0.0001434620401884884</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.730103806229788e-05</v>
+        <v>-0.0006973883595409652</v>
       </c>
       <c r="CO6" t="n">
-        <v>-0.0003629932985852152</v>
+        <v>-0.0007723750677558761</v>
       </c>
       <c r="CP6" t="n">
-        <v>-6.449564189039691e-05</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.0008128099226229285</v>
+        <v>-0.001267801319902714</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.001532305501107536</v>
+        <v>-0.000935790614940879</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0.002430548212044403</v>
+        <v>-0.003861306994875444</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.002942300226794486</v>
+        <v>-0.002789912671421088</v>
       </c>
       <c r="CU6" t="n">
-        <v>-3.355144301568358e-05</v>
+        <v>-8.680265518952457e-05</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0.0001342057720627343</v>
       </c>
       <c r="CW6" t="n">
         <v>0</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0.002259397593255333</v>
+        <v>-0.001721224749597708</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0.0005732590727277719</v>
+        <v>-0.003261906707802987</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.0001634107180307043</v>
+        <v>-0.0002233804914370862</v>
       </c>
       <c r="DA6" t="n">
-        <v>-0.0002356095954857695</v>
+        <v>-0.0002300479964281787</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0.0007846665689583282</v>
+        <v>-0.000646941043740415</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0.001245199979634215</v>
+        <v>-0.00184410634746052</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0.0004024487175778052</v>
+        <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0.0001869079984068489</v>
+        <v>-0.0004909956245477881</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.001369922372301241</v>
+        <v>-0.0005687744317751153</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0.0006160483553063728</v>
+        <v>-0.001476152057017013</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.002261003306093368</v>
+        <v>-0.004641737269139137</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.0009121884533556113</v>
+        <v>-0.0006816687021703126</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.0006346487172009419</v>
+        <v>-0.001108826488139458</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0.001118369060429108</v>
+        <v>-0.0002952084614351591</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0.0001462923218430862</v>
+        <v>-4.838709677420227e-05</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0.00125823212658269</v>
+        <v>-0.001440520177352342</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0.002195531558698419</v>
+        <v>-0.001458839874956561</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.001806242312101655</v>
+        <v>-0.002719515064594569</v>
       </c>
       <c r="DP6" t="n">
-        <v>-0.002550591264450059</v>
+        <v>-0.001667595417097037</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.000103806228373704</v>
+        <v>-0.0003822908407503656</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.0002127726921310108</v>
+        <v>-0.0005202183775852326</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.0003335555594036366</v>
+        <v>-0.0002838958732633956</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0.0019123812275219</v>
+        <v>-0.002496770403577753</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0.00104589407164227</v>
+        <v>-0.001560926485397784</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-0.0002654502293393285</v>
+        <v>-0.0002776643527970219</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.0002177419354838977</v>
+        <v>-0.001030304721509115</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0.002778567620401631</v>
+        <v>-0.003016635033861656</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.0003144058073341866</v>
+        <v>-0.0001646794816969916</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.0001418224946250074</v>
+        <v>-0.0005893287319745949</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.004004335642734206</v>
+        <v>-0.002622792900745313</v>
       </c>
       <c r="EC6" t="n">
-        <v>-0.000854740630429393</v>
+        <v>-0.0005901941317604187</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0.0026413648110026</v>
+        <v>-6.657512177274672e-05</v>
       </c>
       <c r="EE6" t="n">
-        <v>8.392077878482951e-06</v>
+        <v>0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.002683816523751218</v>
+        <v>-0.0009022218789991543</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.001765496662290042</v>
+        <v>-0.0007547990248989084</v>
       </c>
       <c r="EH6" t="n">
-        <v>0</v>
+        <v>-7.537688442211255e-05</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.002478558872435341</v>
+        <v>-0.0006607404109153309</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.000781065218343499</v>
+        <v>-0.001044853188019504</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.0003637799753562043</v>
+        <v>-0.001159110980276734</v>
       </c>
       <c r="EL6" t="n">
-        <v>0</v>
+        <v>-0.0001305217406361969</v>
       </c>
       <c r="EM6" t="n">
-        <v>-2.517623363544886e-05</v>
+        <v>-0.0001258657543777214</v>
       </c>
       <c r="EN6" t="n">
-        <v>2.512562814070418e-05</v>
+        <v>8.326672684688674e-18</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-6.885184286606061e-05</v>
+        <v>8.790436005626235e-06</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0.001444244949919524</v>
+        <v>-0.0007467870788467861</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>-2.595155709342601e-05</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.0001180720759103249</v>
+        <v>-2.512562814070418e-05</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.0001903326428434188</v>
+        <v>-0.001273108418930127</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0.001340739199626287</v>
+        <v>-0.0009740116297956874</v>
       </c>
       <c r="EV6" t="n">
-        <v>-2.605071205279419e-05</v>
+        <v>-0.0002915899376948611</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0.000861602645525858</v>
+        <v>8.683570684273058e-06</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0.00036001522729181</v>
+        <v>-0.000737966899321399</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.0004385219994915535</v>
+        <v>-0.001593017567855051</v>
       </c>
     </row>
     <row r="7">
@@ -3552,442 +3552,442 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0006425842306356011</v>
+        <v>0.0002957966507526333</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0002946464735088305</v>
+        <v>0.0001767979683363063</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002133972947605978</v>
+        <v>-0.0002347420216220475</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0002101400108842688</v>
+        <v>-0.000357573045390136</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0002668019946162947</v>
+        <v>-0.0007404649623562244</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0004954853011255034</v>
+        <v>-0.000335413219167352</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00058656828958486</v>
+        <v>-4.810088101159238e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001027968559617415</v>
+        <v>6.880180252674672e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000651964434321739</v>
+        <v>-0.0004297095035004528</v>
       </c>
       <c r="K7" t="n">
-        <v>1.68516297499588e-05</v>
+        <v>0.000223922669966703</v>
       </c>
       <c r="L7" t="n">
-        <v>5.129958960329861e-05</v>
+        <v>3.350083752093891e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0004164428443011681</v>
+        <v>-0.0005356995118722562</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.001618869379792243</v>
+        <v>-0.000181099817024205</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0009937316129714103</v>
+        <v>-0.0004022055305641703</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0008073557916165874</v>
+        <v>-7.792342724551317e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002692705602410078</v>
+        <v>-0.001217342607802013</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0006371855407810267</v>
+        <v>0.0005217775962978233</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0005800808072439434</v>
+        <v>-0.0009109197714653571</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0001031337355414497</v>
+        <v>0.00011934959796705</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0006763269637790226</v>
+        <v>0.0001665011996359545</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0005732145735042715</v>
+        <v>-0.0001363723632355651</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001546885533057551</v>
+        <v>-0.0004467346685679274</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.207049167134533e-06</v>
+        <v>0.0005906965371728024</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.0002909243450086363</v>
+        <v>0.0001278094875024838</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001726687633400437</v>
+        <v>0.0002655890145283779</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001717368460391932</v>
+        <v>0.001429934329185539</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.0008751475381433671</v>
+        <v>5.345563348857577e-07</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.0007043813164259061</v>
+        <v>0.0004926020224340965</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.005974022627537112</v>
+        <v>0.006273916458920508</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.001940254895397253</v>
+        <v>0.003552889931930803</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0004091399131608942</v>
+        <v>-0.0004689128169503509</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.0001181757487231649</v>
+        <v>-8.694234243590837e-05</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0001370000804699456</v>
+        <v>-0.0001907080385225857</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0003553821989540962</v>
+        <v>-8.443020333571139e-05</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0004567178652444437</v>
+        <v>0.0002800115683237236</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.005540118096561264</v>
+        <v>0.004244037546230517</v>
       </c>
       <c r="AL7" t="n">
-        <v>-7.953277570236227e-05</v>
+        <v>5.210142410561058e-05</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.004295362197883734</v>
+        <v>0.001240557950169141</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.001734735601760412</v>
+        <v>0.0006655817766752393</v>
       </c>
       <c r="AO7" t="n">
-        <v>6.599394929742705e-05</v>
+        <v>0.001092867163037259</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.0002040886381659723</v>
+        <v>-5.191216278296328e-05</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0007789433326402306</v>
+        <v>0.0006425842306356621</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.007219099094505388</v>
+        <v>0.003234846011535569</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.000435161443331572</v>
+        <v>-0.0005198027735184962</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.0009390253991892139</v>
+        <v>-0.0001918869845415838</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.0003623446267370212</v>
+        <v>0.0003396805083623999</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.001146846490836695</v>
+        <v>-0.0002419955323901657</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0004490295930475452</v>
+        <v>-0.0007800760378726679</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0004369570325685968</v>
+        <v>-0.0001570233454513903</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0002761418807199601</v>
+        <v>0.0005056575627797044</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.001113551629113285</v>
+        <v>0.0006464414793523777</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.001159984985826157</v>
+        <v>0.003553042056370243</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.003648007590132807</v>
+        <v>0.004107462454940009</v>
       </c>
       <c r="BC7" t="n">
-        <v>-1.675041876047501e-05</v>
+        <v>-0.0002307588880547717</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.0001389371309482912</v>
+        <v>-0.0001021543704682604</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0006185888854604582</v>
+        <v>-0.0003017785036976195</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.002386679047951512</v>
+        <v>0.001362000496401089</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.001695040388202651</v>
+        <v>0.002795286498467492</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.0003055875855108192</v>
+        <v>0.0001910385550538463</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.002791425206286779</v>
+        <v>-0.000365503208414114</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0008155517670431489</v>
+        <v>0.0001734127303452127</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.001755679007711403</v>
+        <v>-0.0009047686678251676</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0001423503131706916</v>
+        <v>0.0002289133841249236</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.000182692348036384</v>
+        <v>-6.253114532012193e-06</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0003072909943556079</v>
+        <v>0.002604271738438984</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0006800212181724052</v>
+        <v>-0.0001563042723167596</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0002103690903250799</v>
+        <v>-0.0006849649089328668</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0007910195541965037</v>
+        <v>-0.000622224023342538</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.001256515264333602</v>
+        <v>0.0001039384349861894</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.001321241694584768</v>
+        <v>-7.032348804497102e-05</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0.0003631062997345224</v>
+        <v>0.0003453604949330502</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0006322503802066114</v>
+        <v>-0.000442217905796749</v>
       </c>
       <c r="BW7" t="n">
-        <v>-1.61290322580665e-05</v>
+        <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.0008001938397068642</v>
+        <v>0.0008406758968993011</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.0006489519463247273</v>
+        <v>0.0002806097041919364</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.002246189973506468</v>
+        <v>0.0003213415694892197</v>
       </c>
       <c r="CA7" t="n">
-        <v>-0.0001392044091156952</v>
+        <v>0.0002265924985035084</v>
       </c>
       <c r="CB7" t="n">
-        <v>-4.2655326910057e-07</v>
+        <v>0.0003175945948974302</v>
       </c>
       <c r="CC7" t="n">
-        <v>6.529546196542002e-05</v>
+        <v>-0.0001550409830841093</v>
       </c>
       <c r="CD7" t="n">
-        <v>-0.000644915978943672</v>
+        <v>-0.0006290322580645046</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.000150136821281438</v>
+        <v>0.00043072275464201</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.001383357287572035</v>
+        <v>-0.0003641530668892334</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.0005041734693156608</v>
+        <v>-0.0001803418533379563</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0004508004204256344</v>
+        <v>-0.0001352203683881115</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.000498799268845046</v>
+        <v>-0.0002605071205279474</v>
       </c>
       <c r="CJ7" t="n">
         <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0001213055763547188</v>
+        <v>-0.0003123190204351756</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0.0007482543631037507</v>
+        <v>-0.0005382910175735557</v>
       </c>
       <c r="CM7" t="n">
-        <v>-0.0001374311319273236</v>
+        <v>0.0001490013411765412</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0004895195317816625</v>
+        <v>-0.0005337091193213572</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0004118848761108074</v>
+        <v>-0.0001876174864018643</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.612903225806095e-05</v>
+        <v>0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.0004659472983455204</v>
+        <v>-0.0001303052866716226</v>
       </c>
       <c r="CR7" t="n">
-        <v>-6.597018929900274e-05</v>
+        <v>-0.0003253118011095735</v>
       </c>
       <c r="CS7" t="n">
-        <v>-5.333486932176391e-05</v>
+        <v>-0.00221452998209507</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0.0001947173864964569</v>
+        <v>-0.001739961374426652</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-1.61290322580665e-05</v>
       </c>
       <c r="CV7" t="n">
-        <v>5.210142410558838e-05</v>
+        <v>-5.129958960327085e-05</v>
       </c>
       <c r="CW7" t="n">
         <v>0</v>
       </c>
       <c r="CX7" t="n">
-        <v>-3.786411036861281e-05</v>
+        <v>-0.0002906976744185719</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.001153043554308852</v>
+        <v>-0.0001762361813979207</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-8.474915508829283e-05</v>
+        <v>1.736714136854611e-05</v>
       </c>
       <c r="DA7" t="n">
-        <v>-3.350083752095001e-05</v>
+        <v>-0.0001031337355414275</v>
       </c>
       <c r="DB7" t="n">
-        <v>-0.0003258025824933563</v>
+        <v>-0.0002568067848795874</v>
       </c>
       <c r="DC7" t="n">
-        <v>-0.000890122200312421</v>
+        <v>-0.000147886158682875</v>
       </c>
       <c r="DD7" t="n">
-        <v>-5.086797888946837e-05</v>
+        <v>0.0001168263780541745</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.0001042028482111545</v>
+        <v>-5.274261603371855e-05</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.0004521199527878716</v>
+        <v>0.0003402243625974133</v>
       </c>
       <c r="DG7" t="n">
-        <v>-0.0003837951133184581</v>
+        <v>-5.25066387704054e-05</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.0009629990579215874</v>
+        <v>-0.001875849084486936</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.000459033073089149</v>
+        <v>-3.929841978985715e-05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0002330757689311846</v>
+        <v>-0.0006455363840960182</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0.0004461630113410664</v>
+        <v>-7.00515510856925e-05</v>
       </c>
       <c r="DL7" t="n">
-        <v>-3.473428273707557e-05</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.0006185351350811996</v>
+        <v>-0.0002108261614919671</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0.0005224341267744126</v>
+        <v>-0.0001495109958394303</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.001292862764409281</v>
+        <v>-0.001654357712309168</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0.001087056319971286</v>
+        <v>-0.0008012395400223084</v>
       </c>
       <c r="DQ7" t="n">
-        <v>8.253990798799405e-05</v>
+        <v>-1.61290322580665e-05</v>
       </c>
       <c r="DR7" t="n">
-        <v>-8.678502426038849e-05</v>
+        <v>0</v>
       </c>
       <c r="DS7" t="n">
-        <v>-1.675041876046945e-05</v>
+        <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>-0.001006846179969367</v>
+        <v>-0.0007636495870058547</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.0005225187805748543</v>
+        <v>0.0005100040832993202</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>-5.093545288246681e-05</v>
+        <v>-1.709986320108103e-05</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0004682384738073364</v>
+        <v>-0.0006041080535544585</v>
       </c>
       <c r="DY7" t="n">
-        <v>-0.0009506490464227801</v>
+        <v>-0.001343887469115279</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-3.723008190616994e-05</v>
+        <v>-1.665334536937735e-17</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.0004369398133012459</v>
+        <v>0.000118038077999183</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.001946040950541744</v>
+        <v>-0.00156190545552331</v>
       </c>
       <c r="EC7" t="n">
-        <v>-2.258352075443782e-05</v>
+        <v>-0.0001340489854253224</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.0002099018109213868</v>
+        <v>3.473428273707002e-05</v>
       </c>
       <c r="EE7" t="n">
-        <v>3.598218232161998e-05</v>
+        <v>0</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0.0003994442514762386</v>
+        <v>-0.0006786626570659315</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.0007294199374783372</v>
+        <v>-3.007039784454492e-05</v>
       </c>
       <c r="EH7" t="n">
-        <v>1.632386549135778e-05</v>
+        <v>0.0001563042723167707</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0.001609532191254554</v>
+        <v>-0.0001367989056087371</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.0001838592340691225</v>
+        <v>-0.0002902166656084393</v>
       </c>
       <c r="EK7" t="n">
-        <v>-0.0001042028482112156</v>
+        <v>-0.0001969296617733485</v>
       </c>
       <c r="EL7" t="n">
-        <v>0</v>
+        <v>-3.516174402249383e-05</v>
       </c>
       <c r="EM7" t="n">
         <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.0001248126310832653</v>
+        <v>0.0001899694423841025</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.0003525729010276979</v>
+        <v>0.000357326024047061</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0.0008238110565703671</v>
+        <v>-0.0003166144911755098</v>
       </c>
       <c r="ER7" t="n">
         <v>0</v>
@@ -3996,22 +3996,22 @@
         <v>0</v>
       </c>
       <c r="ET7" t="n">
-        <v>6.839945280439075e-05</v>
+        <v>-0.0001845245023371356</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0.0002073422632048405</v>
+        <v>8.416292516831846e-05</v>
       </c>
       <c r="EV7" t="n">
-        <v>0</v>
+        <v>-6.713662302786361e-05</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.0001971660457035562</v>
+        <v>0.000238699195934089</v>
       </c>
       <c r="EX7" t="n">
-        <v>-6.742862186134846e-05</v>
+        <v>-0.0004884172647460439</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.0002580402300957019</v>
+        <v>-0.0008184933541099503</v>
       </c>
     </row>
     <row r="8">
@@ -4021,466 +4021,466 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003566824877295522</v>
+        <v>0.0005807311643154844</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.722841427076633e-05</v>
+        <v>0.0005732331533754104</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004735876906821535</v>
+        <v>0.0002598659285998201</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0002691906912122066</v>
+        <v>0.0002133070187378239</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.602961859848706e-05</v>
+        <v>-0.0006243591447278735</v>
       </c>
       <c r="G8" t="n">
-        <v>3.267038427011704e-05</v>
+        <v>0.001353486640461357</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001954670550275162</v>
+        <v>0.001139711575543981</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003103045620600364</v>
+        <v>0.001070124660725846</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00160954954334194</v>
+        <v>0.0001936033227665168</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0009962088583261252</v>
+        <v>0.0005434679456294972</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005613650391449899</v>
+        <v>0.0002183264351837355</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0008809369427783432</v>
+        <v>0.0005212785494659644</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003222539159072594</v>
+        <v>0.00284669783998398</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003140097664028818</v>
+        <v>0.0005130587105519529</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001197913848506116</v>
+        <v>0.0003729073091057911</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.005664872806941249</v>
+        <v>0.003061129189494924</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001261468786288372</v>
+        <v>0.001956948350100005</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00128189030018647</v>
+        <v>0.002754296774438223</v>
       </c>
       <c r="T8" t="n">
-        <v>6.400705560496989e-05</v>
+        <v>0.0008237496445609948</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001086165558434654</v>
+        <v>0.0005217090926589146</v>
       </c>
       <c r="V8" t="n">
-        <v>0.00219010457805445</v>
+        <v>0.002025578430841754</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003000446478401564</v>
+        <v>-9.222851417207135e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001669867327906563</v>
+        <v>0.002250685522087706</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0003071481757259853</v>
+        <v>0.0004327085042923895</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003226409791361471</v>
+        <v>0.002481752027612358</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.009317401043346565</v>
+        <v>0.003179499867004401</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0006679662711061435</v>
+        <v>0.0004794096308568585</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.002398109346067623</v>
+        <v>0.002369283124483157</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.01049025082855179</v>
+        <v>0.0081345968327731</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.01315378335499003</v>
+        <v>0.01138002777601084</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.001042424043332843</v>
+        <v>0.001442879901808916</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0007103125182640168</v>
+        <v>0.0001823549843695926</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0007549833760949837</v>
+        <v>0.000190866969450304</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.001373200533386118</v>
+        <v>0.0003296811860236893</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.001842432895245594</v>
+        <v>0.0007744170680391238</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.006744029391223119</v>
+        <v>0.008318860715526252</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.001995708485945</v>
+        <v>0.0005400887172649666</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.007230438841284439</v>
+        <v>0.003240138777348642</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.003192656579179301</v>
+        <v>0.001735160709156277</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.003065310169245594</v>
+        <v>0.002891629037860377</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.001174660623671026</v>
+        <v>8.200732631165054e-05</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.007523940302229378</v>
+        <v>0.003443526798139718</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.00978822653409836</v>
+        <v>0.008360343392755409</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.001091981118893348</v>
+        <v>0.0004064421878511498</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.002743835883442147</v>
+        <v>0.000440555969223097</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.002557473019840381</v>
+        <v>0.0006975469512699118</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.001483601572537532</v>
+        <v>0.0005106280902018867</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.001151246167510558</v>
+        <v>0.0008513002855038615</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0005573892386559003</v>
+        <v>-8.68357068426473e-06</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.001484829496562312</v>
+        <v>0.001606581451145836</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.002568972736211481</v>
+        <v>0.001590876513494252</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.004806060343058072</v>
+        <v>0.004669805824154893</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.006278914702665218</v>
+        <v>0.005918616241923436</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.762211550521534e-05</v>
+        <v>0.0003705853458572772</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0006657306682780777</v>
+        <v>-5.053651028981421e-05</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.002378876131914623</v>
+        <v>0.0003877839425554558</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.003912278236334702</v>
+        <v>0.00231768870924563</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.0040218576609901</v>
+        <v>0.00293375864153875</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.001242624412384455</v>
+        <v>0.0004202619245762512</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.003802919360440998</v>
+        <v>0.00284577026609594</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.002486448207966335</v>
+        <v>0.001349049713151165</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0.0001780038545385137</v>
+        <v>0.001311967230573619</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.000581799235845737</v>
+        <v>0.0004209791403778196</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.001217134057383678</v>
+        <v>0.002108339279714949</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.001310974319367214</v>
+        <v>0.004252658053611444</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.002000640947664531</v>
+        <v>0.002027785988767328</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0006750828002359072</v>
+        <v>-0.0002022594256158694</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.001213184417553956</v>
+        <v>-6.790365165832701e-05</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.001953402839247481</v>
+        <v>0.0002218292380243208</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.002642965740696174</v>
+        <v>0.001446075404991379</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.002115370768740648</v>
+        <v>0.001255818701510778</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.001561815538455391</v>
+        <v>6.174678268211498e-05</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.001926837949397847</v>
+        <v>0.001727402207285092</v>
       </c>
       <c r="BY8" t="n">
-        <v>6.508218533086418e-05</v>
+        <v>0.001320419300805084</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.005312422326687185</v>
+        <v>0.003153689157583512</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0007159010925943954</v>
+        <v>0.0007695395683595119</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0006801112042716744</v>
+        <v>0.0008418135186563758</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.001810598668926386</v>
+        <v>-7.630196833420255e-05</v>
       </c>
       <c r="CD8" t="n">
-        <v>-0.0001951211754977728</v>
+        <v>0.00177189440358296</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.001132749932975369</v>
+        <v>0.001137626967295402</v>
       </c>
       <c r="CF8" t="n">
-        <v>4.909488850949879e-05</v>
+        <v>0.0005790027681205511</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0001618172855221645</v>
+        <v>0.0003909158600148954</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.001134275645979507</v>
+        <v>0.0007191350611293418</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0008216890906142998</v>
+        <v>7.104940792162229e-05</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.792256142963578e-05</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.00206175604199064</v>
+        <v>0.0005114142793719578</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0001429810313783475</v>
+        <v>0.0009224377286834118</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.0007796641979181589</v>
+        <v>0.0004625636834692471</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0008880926957715224</v>
+        <v>-8.781826371898044e-06</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.001175485269484624</v>
+        <v>0.0002556385559531582</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0007455285828268017</v>
+        <v>0.0001296182609666408</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.303715810867847e-06</v>
+        <v>0.0002262918670844244</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.002136520308409187</v>
+        <v>-0.0001358691083945068</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.00239862051236287</v>
+        <v>-6.778082212863799e-05</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.001156335554914517</v>
+        <v>-0.0004870932232470065</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>7.911392405064445e-05</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0001256787461982573</v>
+        <v>6.026335685127837e-05</v>
       </c>
       <c r="CW8" t="n">
         <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0009738528348226666</v>
+        <v>0.0005104467261435985</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.002656100546958021</v>
+        <v>0.001086165994216312</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0002214709485264088</v>
+        <v>0.0002875930284333167</v>
       </c>
       <c r="DA8" t="n">
-        <v>5.210142410558838e-05</v>
+        <v>9.295775643336779e-05</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0005538236096121446</v>
+        <v>-4.129341158818079e-05</v>
       </c>
       <c r="DC8" t="n">
-        <v>-1.175181286305061e-05</v>
+        <v>0.0009527333639592821</v>
       </c>
       <c r="DD8" t="n">
-        <v>7.694938440493959e-05</v>
+        <v>0.0002828945788196646</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0006343831465521977</v>
+        <v>0.0007569616753861141</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0006807409934054681</v>
+        <v>0.000833622785689514</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0007120253164556555</v>
+        <v>0.0003754747352021387</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.0002851836721970841</v>
+        <v>4.234146771988354e-05</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.001281049219700403</v>
+        <v>0.0001720910230576189</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.00148141243853673</v>
+        <v>-1.675041876044725e-05</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.001302229535193747</v>
+        <v>0.0005988975617606945</v>
       </c>
       <c r="DL8" t="n">
-        <v>3.42126447984703e-05</v>
+        <v>2.512562814070418e-05</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0002695485066876252</v>
+        <v>0.0006311306202077954</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.0009550242702376809</v>
+        <v>0.0006602864526301406</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.0003462116988516506</v>
+        <v>-0.0006058546468337006</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.001648849864733365</v>
+        <v>0.0006298794020523941</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.000287299766118021</v>
+        <v>0.0001563042723167651</v>
       </c>
       <c r="DR8" t="n">
-        <v>2.448579823702835e-05</v>
+        <v>7.258064516129926e-05</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
       </c>
       <c r="DT8" t="n">
-        <v>2.113107390768197e-05</v>
+        <v>-0.000321649930793258</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.001470013922081601</v>
+        <v>0.0008600486472490343</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0002117231683043369</v>
+        <v>7.815213615840755e-05</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.001076762764848852</v>
+        <v>0.0006317163180236563</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.0003203907227944918</v>
+        <v>-4.622427417937946e-05</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0002076124567473997</v>
+        <v>9.52429563087026e-05</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.001559659041715028</v>
+        <v>0.000214282846348568</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.001186638703569934</v>
+        <v>-0.0003140350133225778</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0005469425261303007</v>
+        <v>0.000484539904878642</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0003252197310655653</v>
+        <v>0.0001999358563808146</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.0001570310673097097</v>
+        <v>9.677419354840454e-05</v>
       </c>
       <c r="EF8" t="n">
-        <v>6.506531683260208e-05</v>
+        <v>-0.0004356746487122781</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0002447139482629728</v>
+        <v>0.0005760057496246834</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0004327903647820819</v>
+        <v>0.0003188848682759121</v>
       </c>
       <c r="EI8" t="n">
-        <v>-0.0003703318804692685</v>
+        <v>0.0003807880956358395</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0003732599003396786</v>
+        <v>0.0003730630228921755</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.000446847656780866</v>
+        <v>0.000199140865618419</v>
       </c>
       <c r="EL8" t="n">
         <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>2.605071205279696e-05</v>
+        <v>8.09727230397822e-05</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0006680974165961445</v>
+        <v>0.0003162784653867545</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.001132042668941194</v>
+        <v>0.0007844970854927608</v>
       </c>
       <c r="EQ8" t="n">
-        <v>2.761970490311181e-05</v>
+        <v>0.0002166890607133099</v>
       </c>
       <c r="ER8" t="n">
         <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>0</v>
+        <v>2.517623363544886e-05</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0003065459244009861</v>
+        <v>-6.88804616145039e-05</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0.0001128864188954609</v>
+        <v>0.0004379827135619796</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>5.676230615443423e-05</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0006086019993374964</v>
+        <v>0.001087978237476225</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0001929912339965922</v>
+        <v>0.0005741699716331261</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.001526177857591254</v>
+        <v>-0.0001805048165453821</v>
       </c>
     </row>
     <row r="9">
@@ -4490,466 +4490,466 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009279731993299789</v>
+        <v>0.007537688442211021</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002244556113902796</v>
+        <v>0.0008190618019358831</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00274261603375523</v>
+        <v>0.0006701414743111589</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005096774193548381</v>
+        <v>0.0005210142410559282</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001675041876046834</v>
+        <v>0.0004862799583188804</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01153178186870439</v>
+        <v>0.005674740484429041</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003248974008207972</v>
+        <v>0.003425605536332132</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01152530779753762</v>
+        <v>0.00421155729676792</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00225806451612901</v>
+        <v>0.005695142378559437</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001846785225718206</v>
+        <v>0.002419955323901657</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009725599166376719</v>
+        <v>0.001176470588235223</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002717795979151216</v>
+        <v>0.002981574539363452</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01959798994974869</v>
+        <v>0.01021775544388607</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004154103852596269</v>
+        <v>0.00475711892797318</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002698961937716204</v>
+        <v>0.003633217993079529</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01820076415422018</v>
+        <v>0.006712802768166071</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003870967741935483</v>
+        <v>0.003551088777219413</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01035175879396981</v>
+        <v>0.005438066465256785</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001580645161290317</v>
+        <v>0.001453287197231767</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002500868357068409</v>
+        <v>0.001040617656931819</v>
       </c>
       <c r="V9" t="n">
+        <v>0.004429065743944594</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.004096774193548402</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.009723183391003398</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.00318898959382341</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.007821416582745867</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.006700167504187582</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.002159344750558389</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.003323262839879138</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.02256055363321796</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.01681139284473778</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.007051059395623516</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.001474036850921223</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.002680067001675002</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.001935964259121303</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.004728220402084815</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.03217993079584772</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.001809045226130623</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.006946856547412328</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.004616530156366305</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.01820069204152244</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.0008190618019358831</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.01310498883097537</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.02288989232372355</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.003403959708232052</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.006901172529313227</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.002283737024221377</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.002500868357068464</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.004656616415410364</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.0008336227856894918</v>
+      </c>
+      <c r="AY9" t="n">
         <v>0.003256126216851285</v>
       </c>
-      <c r="W9" t="n">
-        <v>0.005848153214774321</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.004887482419127942</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.002222994095171915</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.006290322580645135</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.01736714136853072</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0.001306532663316506</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.005778546712802746</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.02499162479061973</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.01718592964824118</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.005770662695457984</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.004008438818565341</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.0009354838709677126</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0.005977496483825562</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.007716262975778532</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.03373702422145326</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0.006118143459915537</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.01080645161290322</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0.006780798925814013</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.0044303797468354</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0.002777777777777724</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0.01524835012156994</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0.0202010050251256</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0.004219409282700382</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0.004120603015075353</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0.004322580645161278</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.003986599664991608</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.001943048576214357</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0.001096774193548378</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0.003369225425494948</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>0.008071135430916587</v>
+        <v>0.003677419354838707</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.01798994974874368</v>
+        <v>0.006097152428810704</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.008828465928163821</v>
+        <v>0.007421340629274997</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001367989056087571</v>
+        <v>0.0006377979187646932</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.002531645569620211</v>
+        <v>0.0007865937072503493</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.008358509566968786</v>
+        <v>0.005303793219201047</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.006968174204355071</v>
+        <v>0.006505190311418651</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.01053351573187417</v>
+        <v>0.004288107202680058</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.003551336146272788</v>
+        <v>0.004623115577889437</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.01587781134608931</v>
+        <v>0.009600537092984196</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.005244876693296252</v>
+        <v>0.001563663440059493</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.004422110552763781</v>
+        <v>0.003651591289782219</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001538987688098503</v>
+        <v>0.002081235313863661</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.002568875651526481</v>
+        <v>0.005025125628140692</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.008777219430485716</v>
+        <v>0.006771545827633407</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.007586438402148343</v>
+        <v>0.006612957368244343</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.001299589603283213</v>
+        <v>0.0009141364675155583</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.004455611390284708</v>
+        <v>0.003201787043931459</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.003516174402250305</v>
+        <v>0.001419354838709652</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.003944636678200641</v>
+        <v>0.004221105527638181</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.003445850914205306</v>
+        <v>0.004740484429065705</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.006469760900140587</v>
+        <v>0.0009467841984982517</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>3.473428273705892e-05</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.002918424753867754</v>
+        <v>0.002064516129032257</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.006225806451612892</v>
+        <v>0.002605071205279619</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.01060191518467854</v>
+        <v>0.005680705190989255</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.002680067001675002</v>
+        <v>0.001809045226130612</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.00588235294117645</v>
+        <v>0.001660899653979164</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.004129032258064524</v>
+        <v>0.0004515456755818215</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.002500868357068409</v>
+        <v>0.006262975778546687</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.002548387096774185</v>
+        <v>0.00412890231621349</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.002193548387096755</v>
+        <v>0.003645161290322585</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0011290322580645</v>
+        <v>0.001943048576214368</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.001516129032258051</v>
+        <v>0.002144053601340001</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.001336146272855077</v>
+        <v>0.001742043551088757</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.000170998632010988</v>
+        <v>6.713662302786361e-05</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.005387096774193534</v>
+        <v>0.001541038525963112</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0007294199374782373</v>
+        <v>0.003548387096774175</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.002546063651591246</v>
+        <v>0.00064516129032256</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.00194511983327541</v>
+        <v>0.001644847264182581</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.003387096774193532</v>
+        <v>0.003618090452261291</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.00179324894514763</v>
+        <v>0.0005904828065300793</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.003645161290322574</v>
+        <v>0.003886097152428802</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.004229607250755297</v>
+        <v>0.003903225806451582</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.007831737346101254</v>
+        <v>0.0009845288326301382</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.002359781121751059</v>
+        <v>0.002322580645161276</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0008087201125175026</v>
+        <v>0.0006042296072507614</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0008387096774193581</v>
+        <v>0.0004516129032258176</v>
       </c>
       <c r="CW9" t="n">
         <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.002646566164154063</v>
+        <v>0.001309164149043274</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.006516129032258044</v>
+        <v>0.003677419354838707</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.000622837370242213</v>
+        <v>0.0006774193548387042</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0004516129032258176</v>
+        <v>0.0005223636957232047</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.001019690576652532</v>
+        <v>0.0007049345417925234</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.00383870967741935</v>
+        <v>0.002853306478684092</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.001290322580645142</v>
+        <v>0.0006713662302786138</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.002316213494461228</v>
+        <v>0.002768166089965329</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.001880984952120413</v>
+        <v>0.001090014064697653</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.003718592964824086</v>
+        <v>0.001806451612903215</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.001722925457102631</v>
+        <v>0.001044727391446332</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.006293952180028073</v>
+        <v>0.002076124567473969</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.005129958960328351</v>
+        <v>0.003625377643504513</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.002918424753867743</v>
+        <v>0.001528308440430726</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0006451612903225712</v>
+        <v>0.0005210142410559393</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0009493670886075334</v>
+        <v>0.001042028482111868</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.009268125854993181</v>
+        <v>0.002735978112175119</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.002804377564979477</v>
+        <v>0.001273031825795612</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.003860355824102046</v>
+        <v>0.001675041876046868</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0006329113924050112</v>
+        <v>0.0003806228373702481</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0006713662302786361</v>
+        <v>0.000484429065743941</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0005210142410558838</v>
+        <v>0.0005536332179930769</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.0007049345417925679</v>
+        <v>0.0003164556962025444</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.003216080402010024</v>
+        <v>0.001665034280117572</v>
       </c>
       <c r="DV9" t="n">
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0008790436005625124</v>
+        <v>0.0003917727717923869</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.003967168262653931</v>
+        <v>0.001474036850921223</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.001526433358153434</v>
+        <v>0.0005625879043600901</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0008727760993622269</v>
+        <v>0.0004699563611950452</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.002512562814070307</v>
+        <v>0.002643335815338743</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.002461322081575212</v>
+        <v>0.001632386549134879</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.002479061976549368</v>
+        <v>0.002114803625377604</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.00274706867671688</v>
+        <v>0.0004844290657439299</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.001225806451612854</v>
+        <v>0.000503524672708966</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.0009715242881071284</v>
+        <v>0.001477005706612933</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.001778385772913826</v>
+        <v>0.001319902744008361</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0009677419354838568</v>
+        <v>0.001799307958477436</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.005326633165829065</v>
+        <v>0.001762977473065663</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.001072026800669956</v>
+        <v>0.001116902457185331</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.002780569514237818</v>
+        <v>0.003289694528365206</v>
       </c>
       <c r="EL9" t="n">
-        <v>3.35683115139318e-05</v>
+        <v>0.0001042028482111879</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0005882352941176561</v>
+        <v>0.000449826989619373</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.001225806451612876</v>
+        <v>0.0007612456747404517</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.001741935483870949</v>
+        <v>0.001903225806451592</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.001909547738693407</v>
+        <v>0.003499627699180907</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0001612903225806539</v>
+        <v>3.264773098270446e-05</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.00116129032258061</v>
+        <v>0.0001958863858962267</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.0008727760993622157</v>
+        <v>0.00100729419937482</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.002546063651591246</v>
+        <v>0.001840916985064267</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.000246132208157468</v>
+        <v>0.001303052866716226</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.002222982216142277</v>
+        <v>0.001945119833275466</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.003082077051926269</v>
+        <v>0.001943048576214346</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.002359781121751048</v>
+        <v>0.0004838709677419173</v>
       </c>
     </row>
   </sheetData>
